--- a/results/Int Task Remove ACC -0.1/Rando_fi_explain.xlsx
+++ b/results/Int Task Remove ACC -0.1/Rando_fi_explain.xlsx
@@ -1148,268 +1148,268 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.147102947376292e-05</v>
+        <v>-0.0001743739953289491</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.004241975019407958</v>
+        <v>-0.007028195881828113</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0026521509863838</v>
+        <v>0.0006480696203834147</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0008798010806427813</v>
+        <v>-0.001421287102158578</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001711086095278911</v>
+        <v>-0.0002248905240443422</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001015954862497024</v>
+        <v>0.003468494891042549</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0002426156033918758</v>
+        <v>-1.461121864201333e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.00315509735102032</v>
+        <v>-0.001301043382527561</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01595455657828437</v>
+        <v>0.01827808714775506</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01807666641489845</v>
+        <v>0.02032899064237234</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0004859482922980961</v>
+        <v>-0.001495614135654454</v>
       </c>
       <c r="N3" t="n">
-        <v>0.001360864280521684</v>
+        <v>0.0004095304881751784</v>
       </c>
       <c r="O3" t="n">
-        <v>0.003946453829202972</v>
+        <v>0.002455240513538709</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01129287256989755</v>
+        <v>0.01159162618952084</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.009681366965669054</v>
+        <v>0.007045001051783496</v>
       </c>
       <c r="R3" t="n">
-        <v>0.002016613308797709</v>
+        <v>8.558867405127138e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>0.001447276258295923</v>
+        <v>0.0004809154878826627</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0008279586855668118</v>
+        <v>-0.0006587638356438405</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0009556416012648326</v>
+        <v>0.00100207773951398</v>
       </c>
       <c r="V3" t="n">
-        <v>-8.047073497297829e-05</v>
+        <v>-3.232729830098812e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>0.002414041333270618</v>
+        <v>0.002626918359878724</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.002411586643144221</v>
+        <v>-0.002694885562249431</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.001468623947619703</v>
+        <v>0.001601910095733744</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0002576389255248924</v>
+        <v>0.000153907751210829</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.0008141517514550833</v>
+        <v>-0.002070296784196817</v>
       </c>
       <c r="AB3" t="n">
-        <v>-9.027064585219401e-05</v>
+        <v>-1.681452948661956e-05</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.002813064013148797</v>
+        <v>0.002587966340886861</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.004700769937782773</v>
+        <v>-0.004750439202664314</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.00210887660376545</v>
+        <v>-0.004191095356033949</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.003630025539310512</v>
+        <v>-0.004127185126527101</v>
       </c>
       <c r="AG3" t="n">
-        <v>4.910438241012227e-05</v>
+        <v>0.000104579640881175</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.0002050044780170579</v>
+        <v>-0.0003558737917333676</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0.002497517742101818</v>
+        <v>-0.005014938777846261</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.004941389339060706</v>
+        <v>-0.004499012089291267</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0.0005885368114130153</v>
+        <v>-1.987611409873025e-05</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0.0002862275690559446</v>
+        <v>-0.0002286667045507551</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.001456371725290636</v>
+        <v>0.001140694789741682</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.002129515696475093</v>
+        <v>-0.001487015528346693</v>
       </c>
       <c r="AP3" t="n">
-        <v>8.050814797377903e-07</v>
+        <v>-0.0002679418350804419</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.001087141750764117</v>
+        <v>0.0005304166378428265</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0.002117220900423918</v>
+        <v>-0.003104191312978176</v>
       </c>
       <c r="AS3" t="n">
-        <v>-9.395145630280203e-05</v>
+        <v>0.001395275438001809</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0.001820919583913662</v>
+        <v>-0.003886598816155201</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.002987537507995945</v>
+        <v>-0.0009829923961913445</v>
       </c>
       <c r="AV3" t="n">
-        <v>5.389020997525027e-05</v>
+        <v>-0.002177431133383419</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.0005091140375609095</v>
+        <v>-0.002555227648421573</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.0007160929341499034</v>
+        <v>0.0004055688964425009</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.001548149118621919</v>
+        <v>-0.001310887971665253</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-0.0012648514329108</v>
+        <v>-0.002776125733601698</v>
       </c>
       <c r="BA3" t="n">
-        <v>-0.001220456999176385</v>
+        <v>-0.001531848744188628</v>
       </c>
       <c r="BB3" t="n">
-        <v>-0.002534061265774935</v>
+        <v>-0.004096397912247151</v>
       </c>
       <c r="BC3" t="n">
-        <v>-0.000336998052414359</v>
+        <v>0.0004016588262731957</v>
       </c>
       <c r="BD3" t="n">
-        <v>6.031910690745599e-05</v>
+        <v>3.57859204415656e-05</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.0001975144022197684</v>
+        <v>-0.000729858798146542</v>
       </c>
       <c r="BF3" t="n">
-        <v>-0.006677739046026481</v>
+        <v>-0.007162808885565792</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.002961795845082746</v>
+        <v>-0.0005056181154372862</v>
       </c>
       <c r="BH3" t="n">
         <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.0002013604172491934</v>
+        <v>0.0005615122789625426</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.001111863757012579</v>
+        <v>-0.001404462749056255</v>
       </c>
       <c r="BK3" t="n">
-        <v>-0.003227513156563182</v>
+        <v>-0.004997295414938973</v>
       </c>
       <c r="BL3" t="n">
-        <v>-6.589205295959526e-05</v>
+        <v>-1.627958631351652e-06</v>
       </c>
       <c r="BM3" t="n">
-        <v>-0.0002210273899832426</v>
+        <v>-0.002509133494913922</v>
       </c>
       <c r="BN3" t="n">
-        <v>-0.003954662627270609</v>
+        <v>-0.002431131419899147</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.00192250024798677</v>
+        <v>-0.001687374659097312</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0.001436601108316591</v>
+        <v>-0.001406806340282288</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.000111678406695086</v>
+        <v>-6.564350205202296e-05</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.0001423920027721271</v>
+        <v>-0.001121633741256587</v>
       </c>
       <c r="BS3" t="n">
-        <v>-0.0006956863511450784</v>
+        <v>-0.0008675868804140752</v>
       </c>
       <c r="BT3" t="n">
-        <v>-6.17560333317624e-05</v>
+        <v>-0.001312668778335903</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.006135294677612907</v>
+        <v>0.005333448635065792</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0.001206624451821927</v>
+        <v>-0.0007178835111876958</v>
       </c>
       <c r="BW3" t="n">
-        <v>-6.657557365000321e-05</v>
+        <v>0.001171086228857541</v>
       </c>
       <c r="BX3" t="n">
-        <v>-9.287288380198873e-05</v>
+        <v>0.0002464301953803871</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.0002109803703323254</v>
+        <v>3.024540807492372e-05</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.000314021099768811</v>
+        <v>0.0001155056272058386</v>
       </c>
       <c r="CA3" t="n">
-        <v>6.891798759474099e-06</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.0006273232825040531</v>
+        <v>-0.0002179056754256337</v>
       </c>
       <c r="CC3" t="n">
-        <v>-0.00155592755107785</v>
+        <v>-0.001102943991050489</v>
       </c>
       <c r="CD3" t="n">
-        <v>-4.359043539846508e-05</v>
+        <v>3.47837451601607e-05</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.0004916372624410826</v>
+        <v>0.0008612904731806713</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0.0003984744706593569</v>
+        <v>-0.002344306868720969</v>
       </c>
       <c r="CG3" t="n">
-        <v>-0.0006867880287006599</v>
+        <v>0.0005384345067619199</v>
       </c>
       <c r="CH3" t="n">
-        <v>-0.0006632758842038811</v>
+        <v>-0.0002840417270337459</v>
       </c>
       <c r="CI3" t="n">
-        <v>-0.002510028904792112</v>
+        <v>0.0003526882565984291</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.0007903979484495248</v>
+        <v>-0.002182639624036011</v>
       </c>
       <c r="CK3" t="n">
-        <v>-0.001037958215921632</v>
+        <v>0.001042778286690753</v>
       </c>
     </row>
     <row r="4">
@@ -1419,268 +1419,268 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003699973583596533</v>
+        <v>0.003827576282942164</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01003892210037047</v>
+        <v>0.008391569351772569</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004823495329188019</v>
+        <v>0.004351662334076543</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00333623624266491</v>
+        <v>0.00592653237329488</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004218703498260798</v>
+        <v>0.004471761414815053</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00516472055631052</v>
+        <v>0.006457735917796013</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0004067004182273446</v>
+        <v>0.0002843020775747129</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002444099727344473</v>
+        <v>0.005872161326352166</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02507085039958878</v>
+        <v>0.01806468418156542</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02382433770083311</v>
+        <v>0.02445043932321183</v>
       </c>
       <c r="M4" t="n">
-        <v>0.005573220132001596</v>
+        <v>0.008121583889771007</v>
       </c>
       <c r="N4" t="n">
-        <v>0.002366463532473261</v>
+        <v>0.00462954956123274</v>
       </c>
       <c r="O4" t="n">
-        <v>0.006781615240797592</v>
+        <v>0.006053800872484839</v>
       </c>
       <c r="P4" t="n">
-        <v>0.02349885800513139</v>
+        <v>0.02230998179463854</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.01173606955316008</v>
+        <v>0.0145172497665505</v>
       </c>
       <c r="R4" t="n">
-        <v>0.003346980166784087</v>
+        <v>0.005459804783639256</v>
       </c>
       <c r="S4" t="n">
-        <v>0.002619595047408668</v>
+        <v>0.003616821652136673</v>
       </c>
       <c r="T4" t="n">
-        <v>0.006580796933868621</v>
+        <v>0.006896018191560805</v>
       </c>
       <c r="U4" t="n">
-        <v>0.002887195908143307</v>
+        <v>0.003517616964315888</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0002747204284391956</v>
+        <v>0.0003430206584482204</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0122355711919026</v>
+        <v>0.01416847739488703</v>
       </c>
       <c r="X4" t="n">
-        <v>0.006182214051242052</v>
+        <v>0.004735827491813915</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.003556034239051392</v>
+        <v>0.003733972512979653</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0013567779866506</v>
+        <v>0.003029586770012513</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.003365653145863634</v>
+        <v>0.003756005921616012</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0004420448499665305</v>
+        <v>0.000615912048440365</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.007486228146624489</v>
+        <v>0.006994929631742672</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.009021699856893824</v>
+        <v>0.01102493717673889</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.005111523496621091</v>
+        <v>0.006736406007503561</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.008251793306905083</v>
+        <v>0.00731869184405317</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.0006280182098084219</v>
+        <v>0.0007023438001179924</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.0009824412550212462</v>
+        <v>0.0005435594527001165</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.005836225677960286</v>
+        <v>0.006249238239897619</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.006939262929976082</v>
+        <v>0.008867883447829173</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.001111964815890536</v>
+        <v>0.0005184109806162876</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.0008251386849190776</v>
+        <v>0.001458408936103731</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.003105479063148909</v>
+        <v>0.004574262548558719</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.005127065357642891</v>
+        <v>0.004557340808028972</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.0009689048250574379</v>
+        <v>0.001263554435637337</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.00289631665420201</v>
+        <v>0.003762106283684855</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.004086058296391023</v>
+        <v>0.006020237706666146</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.003276072539781828</v>
+        <v>0.00415801223154306</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.006024302761175263</v>
+        <v>0.003016166253420699</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.005016379790090847</v>
+        <v>0.004527363669894818</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.001731361703955515</v>
+        <v>0.003722888291004431</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.004681701595334185</v>
+        <v>0.003189032764960703</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.001401633562712005</v>
+        <v>0.0008294964578877984</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.003308447065320104</v>
+        <v>0.002102823236306936</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.007359718252767355</v>
+        <v>0.008110011397768664</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.01099510209987191</v>
+        <v>0.006151088106547476</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.008375334945126425</v>
+        <v>0.008305711168120705</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.0007253025198827018</v>
+        <v>0.001388515284250541</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.001000197369308131</v>
+        <v>0.0007502746814798323</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.001077295550690049</v>
+        <v>0.0008499311415861307</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.008313654545421845</v>
+        <v>0.01301440055671963</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.009681094231013669</v>
+        <v>0.006602330004998754</v>
       </c>
       <c r="BH4" t="n">
         <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.001404729499758252</v>
+        <v>0.001057137965900531</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.00213849469640898</v>
+        <v>0.003891600899432016</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.008729856379709855</v>
+        <v>0.005835538292851971</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.001002899650313479</v>
+        <v>0.0005318905096715825</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.003751227149957369</v>
+        <v>0.005005415580788937</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.01028206939043432</v>
+        <v>0.005117527793958945</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.006674246975516768</v>
+        <v>0.004711751138206382</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.004780011088160136</v>
+        <v>0.004102983923239338</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.0003933874390873053</v>
+        <v>0.0002058658467478763</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.00411562648651143</v>
+        <v>0.00383620914980244</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.004011565024123661</v>
+        <v>0.004300157832840178</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.0014303312554056</v>
+        <v>0.001014832865663489</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.007842246008397601</v>
+        <v>0.00969331450990002</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.003999697423010307</v>
+        <v>0.003022558806281268</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.007584241756603978</v>
+        <v>0.004850372454611369</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.0002167974541113068</v>
+        <v>0.0002781542853438701</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.001353952618594746</v>
+        <v>0.001785770902791943</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.002156510306379219</v>
+        <v>0.001170904845620008</v>
       </c>
       <c r="CA4" t="n">
-        <v>2.179378125546109e-05</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.001309104281078224</v>
+        <v>0.001080460010091443</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.00340808184501229</v>
+        <v>0.00450289056080791</v>
       </c>
       <c r="CD4" t="n">
-        <v>9.224331005064555e-05</v>
+        <v>0.0001330358096412641</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.001189982777178628</v>
+        <v>0.001432626381160027</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.003006274354376304</v>
+        <v>0.002773501147092541</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.003693669560267621</v>
+        <v>0.00250319611873161</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.001662028962263464</v>
+        <v>0.001567136602449507</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.004746559169146637</v>
+        <v>0.002477146783968477</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.004390322574642037</v>
+        <v>0.006353632766314452</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.003769627064114999</v>
+        <v>0.003923483795774767</v>
       </c>
     </row>
     <row r="5">
@@ -1690,268 +1690,268 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.003297466157584183</v>
+        <v>-0.008816383200277644</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.02815436241610731</v>
+        <v>-0.02090604026845635</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.002413904087544283</v>
+        <v>-0.008368200836820116</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.009330143540669833</v>
+        <v>-0.01515931766977794</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.003526970954356923</v>
+        <v>-0.004956549726424242</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.006523247744621763</v>
+        <v>-0.008593498551657563</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0002574831026714075</v>
+        <v>-0.0003816793893130055</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.006699062825407842</v>
+        <v>-0.01329399514057616</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.03188757807078415</v>
+        <v>-0.009458128078817718</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.01484400656814447</v>
+        <v>-0.01943095072866069</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.007740367927802827</v>
+        <v>-0.02138146476917733</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.00254264563887997</v>
+        <v>-0.007853234631477335</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.002489626556016644</v>
+        <v>-0.007112970711297106</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.04484553974314472</v>
+        <v>-0.04311003123915304</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.005809128630705473</v>
+        <v>-0.006639004149377648</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.001340033500837545</v>
+        <v>-0.01174766655938206</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.004538139684583209</v>
+        <v>-0.007016414547795347</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.01742450538007637</v>
+        <v>-0.01836167997223184</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.00352348993288587</v>
+        <v>-0.004602510460251075</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.0006282722513088812</v>
+        <v>-0.0005471515931767424</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.01949748743718593</v>
+        <v>-0.02542713567839194</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.01023594725884797</v>
+        <v>-0.010621312044429</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.005025125628140737</v>
+        <v>-0.00579406631762659</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.001570680628272214</v>
+        <v>-0.006465661641541031</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.0080737018425461</v>
+        <v>-0.01043630017452011</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.0008375209380234727</v>
+        <v>-0.001012216404886612</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.006891798759476287</v>
+        <v>-0.005661641541038509</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.01891047883414293</v>
+        <v>-0.02044429017702185</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.01273421235253294</v>
+        <v>-0.01416174939257198</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.0167358229598894</v>
+        <v>-0.01294689343977783</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.001005025125628167</v>
+        <v>-0.001137146795313548</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.001417704011065013</v>
+        <v>-0.001561415683553113</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.01148507980569045</v>
+        <v>-0.01319600901190863</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.01911866759195001</v>
+        <v>-0.02443595973620267</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.002529049897470914</v>
+        <v>-0.0009336099585062207</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0.002081887578070751</v>
+        <v>-0.002315436241610713</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.00471204188481672</v>
+        <v>-0.004851657940663201</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.01061762664816096</v>
+        <v>-0.007060755336617363</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.001675392670157039</v>
+        <v>-0.001705825555197982</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.003283082077051957</v>
+        <v>-0.008237347294938958</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.01110340041637747</v>
+        <v>-0.01732037486983682</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0.003087248322147618</v>
+        <v>-0.00614093959731542</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0.008986814712005497</v>
+        <v>-0.008866995073891581</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.005794587092296988</v>
+        <v>-0.007499195365304201</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.002767943353717417</v>
+        <v>-0.01107177341486968</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.003636948825233366</v>
+        <v>-0.008786610878661106</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.001457827143352963</v>
+        <v>-0.0005235602094241232</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.005025125628140737</v>
+        <v>-0.005171815341895147</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.01400414937759342</v>
+        <v>-0.02072249589490967</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0.02430213464696223</v>
+        <v>-0.0160591133004926</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0.01599343185550082</v>
+        <v>-0.02082101806239734</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0.001780104712041852</v>
+        <v>-0.001240523776705682</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.001208053691275124</v>
+        <v>-0.001241610738255017</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.002151283830673078</v>
+        <v>-0.00197847969455045</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.02397372742200328</v>
+        <v>-0.04085385878489324</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.02147783251231525</v>
+        <v>-0.01309945284840686</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0.001619572708476935</v>
+        <v>-0.0006375838926174215</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-0.001641454779530127</v>
+        <v>-0.009338387319090258</v>
       </c>
       <c r="BK5" t="n">
-        <v>-0.02220032840722497</v>
+        <v>-0.01934318555008208</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0.001665510062456588</v>
+        <v>-0.0006365159128978281</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.005670816044260119</v>
+        <v>-0.01433530024297116</v>
       </c>
       <c r="BN5" t="n">
-        <v>-0.03057471264367814</v>
+        <v>-0.0129392446633826</v>
       </c>
       <c r="BO5" t="n">
-        <v>-0.007365145228215852</v>
+        <v>-0.01134628730048584</v>
       </c>
       <c r="BP5" t="n">
-        <v>-0.01203007518796989</v>
+        <v>-0.007718814610613367</v>
       </c>
       <c r="BQ5" t="n">
-        <v>-0.0003816793893129833</v>
+        <v>-0.000344589937973816</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0.005536912751677803</v>
+        <v>-0.009249563699825524</v>
       </c>
       <c r="BS5" t="n">
-        <v>-0.007651006711409347</v>
+        <v>-0.006758931445123939</v>
       </c>
       <c r="BT5" t="n">
-        <v>-0.002607016414547791</v>
+        <v>-0.003366886497743804</v>
       </c>
       <c r="BU5" t="n">
-        <v>-0.004617505168849134</v>
+        <v>-0.01127399650959865</v>
       </c>
       <c r="BV5" t="n">
-        <v>-0.008509911141490068</v>
+        <v>-0.005977011494252837</v>
       </c>
       <c r="BW5" t="n">
-        <v>-0.007518796992481191</v>
+        <v>-0.004087544254908304</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0.0005369127516778094</v>
+        <v>-0.0002074688796680491</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.001071922544951587</v>
+        <v>-0.003054187192118196</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0.001619572708476935</v>
+        <v>-0.001860785665058506</v>
       </c>
       <c r="CA5" t="n">
         <v>0</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0.0006711409395972701</v>
+        <v>-0.002266009852216733</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0.00848167539267014</v>
+        <v>-0.01113438045375221</v>
       </c>
       <c r="CD5" t="n">
-        <v>-0.0002348993288590173</v>
+        <v>-0.0002013422818791688</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.001151832460732949</v>
+        <v>-0.001171605789110941</v>
       </c>
       <c r="CF5" t="n">
-        <v>-0.003769633507853376</v>
+        <v>-0.008551483420593387</v>
       </c>
       <c r="CG5" t="n">
-        <v>-0.006903622693096368</v>
+        <v>-0.003839441535776656</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.004473768908915399</v>
+        <v>-0.003711001642036083</v>
       </c>
       <c r="CI5" t="n">
-        <v>-0.008612440191387538</v>
+        <v>-0.002827225130890099</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0.007822191592005544</v>
+        <v>-0.01357684355616813</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0.009090909090909061</v>
+        <v>-0.006282540784449797</v>
       </c>
     </row>
     <row r="6">
@@ -1961,268 +1961,268 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.00294654255491498</v>
+        <v>-0.00146563999211379</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.006597530463276269</v>
+        <v>-0.01278093466603984</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.001380304180851696</v>
+        <v>-0.001800833496267015</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.001312930976526125</v>
+        <v>-0.002060404461892504</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.001787983021198791</v>
+        <v>-0.003920895172956779</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.001970786603336991</v>
+        <v>-0.0002191169311252239</v>
       </c>
       <c r="I6" t="n">
-        <v>5.551115123125783e-18</v>
+        <v>-0.0002341632301234298</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.004837423587623188</v>
+        <v>-0.002078483110083823</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0103950316711053</v>
+        <v>0.006156075413513271</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002588017620840208</v>
+        <v>0.007820445554212633</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.003828533860675248</v>
+        <v>-0.003621394620569876</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0006147192724978795</v>
+        <v>-0.0009271728098620951</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0005319494711690159</v>
+        <v>-0.001047583666084176</v>
       </c>
       <c r="P6" t="n">
-        <v>0.007741215910689258</v>
+        <v>0.007487506450238807</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.004484926518024771</v>
+        <v>0.0004209742005750305</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.0002781104369112497</v>
+        <v>-0.001535914947686076</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0005720058221633268</v>
+        <v>-0.001124190355716406</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.00184249169699052</v>
+        <v>-0.001577894893952381</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.000638435228147638</v>
+        <v>-0.0009542677250097221</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.0002278629873403437</v>
+        <v>-0.0001648281437092752</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.002151238711780534</v>
+        <v>-0.00391746986111155</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.007183094862436782</v>
+        <v>-0.005461219063682246</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.0005080616410869654</v>
+        <v>0.00112976709272504</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.0006817582148399364</v>
+        <v>-0.001061676730490927</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.001202613776624931</v>
+        <v>-0.003193158001609531</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.0002685642596244126</v>
+        <v>-0.0004459072470225423</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.0007288555465757185</v>
+        <v>-0.0007884595035002828</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.01013588547125752</v>
+        <v>-0.01360239323922145</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.004313008508143585</v>
+        <v>-0.008193453740468754</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.01021724739724377</v>
+        <v>-0.009992606322545883</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.000318444929818662</v>
+        <v>-8.987763083484756e-05</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.0003250286294647547</v>
+        <v>-0.0005659763587113008</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0.006039931957633629</v>
+        <v>-0.009271548263095404</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0.008329986089000121</v>
+        <v>-0.008433076862171582</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.0009574925235222798</v>
+        <v>-0.0002624243063119841</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0.0006839521274837084</v>
+        <v>-0.001139624936378916</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.0001388406803193187</v>
+        <v>-0.001805165661757779</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.005979446820209933</v>
+        <v>-0.00422153572817022</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.0004509556622255051</v>
+        <v>-0.0008935339602039905</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.0001879923126378802</v>
+        <v>-9.327835282714193e-05</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.003332382886895113</v>
+        <v>-0.003624979791992261</v>
       </c>
       <c r="AS6" t="n">
-        <v>-0.002245731114005764</v>
+        <v>-0.0003748844294008985</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0.006487231375307431</v>
+        <v>-0.005607484660298704</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.0005649494915661967</v>
+        <v>-0.004043400006153363</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.0007566348269236078</v>
+        <v>-0.003459668054467735</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.00240040417214459</v>
+        <v>-0.004280662378949199</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.0001211239623010646</v>
+        <v>-0.0001280075232640649</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.0002832144488562726</v>
+        <v>-0.002418931157786114</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0.00531370415510965</v>
+        <v>-0.005014496231160334</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0.006539137553827732</v>
+        <v>-0.003009558541930049</v>
       </c>
       <c r="BB6" t="n">
-        <v>-0.006301818912305026</v>
+        <v>-0.005831335578212435</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0.0004149592772777794</v>
+        <v>-0.0007981768846169857</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.0007140348678852021</v>
+        <v>-0.0004342648137614591</v>
       </c>
       <c r="BE6" t="n">
-        <v>-3.560560218193177e-05</v>
+        <v>-0.001367184442716809</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.01015638279124818</v>
+        <v>-0.009225511927000137</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.005655624060480147</v>
+        <v>-0.002732990220890205</v>
       </c>
       <c r="BH6" t="n">
         <v>0</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0.0004237476063510576</v>
+        <v>-9.495787971269542e-05</v>
       </c>
       <c r="BJ6" t="n">
-        <v>-0.0005756718298537689</v>
+        <v>-0.00348376101394362</v>
       </c>
       <c r="BK6" t="n">
-        <v>-0.007001133381566455</v>
+        <v>-0.006775108343259145</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0.0006227739752377864</v>
+        <v>-0.0004668593760598999</v>
       </c>
       <c r="BM6" t="n">
-        <v>-0.002391341968937091</v>
+        <v>-0.002541628314654521</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0.004999711650190281</v>
+        <v>-0.005061127336567342</v>
       </c>
       <c r="BO6" t="n">
-        <v>-0.000362414207405315</v>
+        <v>-0.003474177168565371</v>
       </c>
       <c r="BP6" t="n">
-        <v>-0.003198376999683869</v>
+        <v>-0.004131784577336986</v>
       </c>
       <c r="BQ6" t="n">
-        <v>-8.65268333659186e-05</v>
+        <v>-0.0002080087882723236</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0.003381239152633489</v>
+        <v>-0.001875380232197002</v>
       </c>
       <c r="BS6" t="n">
-        <v>-0.002408685898138036</v>
+        <v>-0.003162138772418102</v>
       </c>
       <c r="BT6" t="n">
-        <v>-0.000675990526712858</v>
+        <v>-0.001832385038991524</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0.0004496358856372812</v>
+        <v>0.002700424872077637</v>
       </c>
       <c r="BV6" t="n">
-        <v>-0.002842914433856728</v>
+        <v>-0.002692625036271845</v>
       </c>
       <c r="BW6" t="n">
-        <v>-0.004801512859448367</v>
+        <v>-0.002884704121265469</v>
       </c>
       <c r="BX6" t="n">
-        <v>-0.0002116937235854016</v>
+        <v>5.22106380310694e-05</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.0007188915542688773</v>
+        <v>-0.0006419574897971263</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0.0006968529655773797</v>
+        <v>-0.0001897295599563364</v>
       </c>
       <c r="CA6" t="n">
         <v>0</v>
       </c>
       <c r="CB6" t="n">
-        <v>-0.0002538340480306295</v>
+        <v>-0.0006351532781633084</v>
       </c>
       <c r="CC6" t="n">
-        <v>-0.003619767165869378</v>
+        <v>-0.002199434019507707</v>
       </c>
       <c r="CD6" t="n">
         <v>0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.0004224775783634671</v>
+        <v>0.000292013114281342</v>
       </c>
       <c r="CF6" t="n">
-        <v>-0.002524768032934971</v>
+        <v>-0.003270440771233782</v>
       </c>
       <c r="CG6" t="n">
-        <v>-0.001113607456369006</v>
+        <v>-0.0007803343216203241</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.00101758955974518</v>
+        <v>-0.0008189334592061088</v>
       </c>
       <c r="CI6" t="n">
-        <v>-0.006470244228466457</v>
+        <v>-0.001498561510460231</v>
       </c>
       <c r="CJ6" t="n">
-        <v>-0.001191630313289144</v>
+        <v>-0.004916444830598651</v>
       </c>
       <c r="CK6" t="n">
-        <v>-0.002534348985403795</v>
+        <v>-0.0009898766764470908</v>
       </c>
     </row>
     <row r="7">
@@ -2232,268 +2232,268 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.00097082692962151</v>
+        <v>0.0002054026520991403</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.002769377373969239</v>
+        <v>-0.00793198491724203</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001923031558887867</v>
+        <v>0.001692524122144678</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0001904826221620637</v>
+        <v>-0.000214750597772606</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001151041849678514</v>
+        <v>-0.001365538909113079</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001166861419191662</v>
+        <v>0.004454236892652719</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001738525395616974</v>
+        <v>-3.445899379739825e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.002961328172138828</v>
+        <v>0.0009160833117275835</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01492354282537728</v>
+        <v>0.01924544335808851</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01831083035767465</v>
+        <v>0.01469196164310167</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0007199749265853151</v>
+        <v>0.00123333504196747</v>
       </c>
       <c r="N7" t="n">
-        <v>0.001357795689858704</v>
+        <v>0.0002394353480835054</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0002912816392125595</v>
+        <v>0.001905232671475132</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01274324260935767</v>
+        <v>0.0137083885497454</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.006999862625786823</v>
+        <v>0.004911192547255578</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0008825854738395977</v>
+        <v>2.871005613873655e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>0.001683112044958962</v>
+        <v>0.001604904997078382</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0006224125966163452</v>
+        <v>0.0003701805621858401</v>
       </c>
       <c r="U7" t="n">
-        <v>0.001112470037490632</v>
+        <v>0.000803710948478431</v>
       </c>
       <c r="V7" t="n">
-        <v>-5.204718945177045e-05</v>
+        <v>-8.636999457557472e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>0.001004146018162061</v>
+        <v>0.00355434039644561</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.002788102945116733</v>
+        <v>-0.001813850075284218</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.001133691570126311</v>
+        <v>0.001931086275336735</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0002055798761303185</v>
+        <v>0.0003069725923232347</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0002253363799092356</v>
+        <v>-0.001046194365683656</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.0001516308105718567</v>
+        <v>-6.84389094565363e-05</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.001147108293889898</v>
+        <v>0.0008360669983271896</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0.004048034304118786</v>
+        <v>-0.001645574997166316</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.001668875323151775</v>
+        <v>-0.004912986899035882</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.002223355285380446</v>
+        <v>-0.003713369302750341</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.0001344578271821717</v>
+        <v>0.0001519356658883364</v>
       </c>
       <c r="AH7" t="n">
-        <v>3.844906524770321e-05</v>
+        <v>-0.0003254290939132987</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0.004210309433471887</v>
+        <v>-0.005934770298996533</v>
       </c>
       <c r="AK7" t="n">
-        <v>-0.001526405832237188</v>
+        <v>-0.002641392430873086</v>
       </c>
       <c r="AL7" t="n">
-        <v>-0.0006369936932986986</v>
+        <v>-3.445899379738715e-05</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0.000203986831514269</v>
+        <v>-0.0007398851722357158</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.00184067132659409</v>
+        <v>0.0004831084848398448</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.0002723961605007541</v>
+        <v>-0.001441272788484099</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.0002029781996561175</v>
+        <v>-0.0004979832710681753</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.001143851331012607</v>
+        <v>0.001285444286485737</v>
       </c>
       <c r="AR7" t="n">
-        <v>-0.0008317468472890276</v>
+        <v>-0.001757402569720262</v>
       </c>
       <c r="AS7" t="n">
-        <v>-0.0006825882826112905</v>
+        <v>0.001387688007357341</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0.002969440295883791</v>
+        <v>-0.004642367507530165</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.003046303990833376</v>
+        <v>-0.00146450723638869</v>
       </c>
       <c r="AV7" t="n">
-        <v>6.904357573596643e-05</v>
+        <v>-0.000918873634279227</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0.001006618902030054</v>
+        <v>-0.0019474335025915</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.0005111073290003821</v>
+        <v>8.34143375798957e-05</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.002059352477112431</v>
+        <v>-0.001420969473160655</v>
       </c>
       <c r="AZ7" t="n">
-        <v>-0.001971086979391312</v>
+        <v>-0.00228437937544731</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.00130332196012477</v>
+        <v>-0.0007269229417758926</v>
       </c>
       <c r="BB7" t="n">
-        <v>-0.002629440931734189</v>
+        <v>-0.003844992469897235</v>
       </c>
       <c r="BC7" t="n">
-        <v>-0.0002910005148286765</v>
+        <v>0.0002682877474621648</v>
       </c>
       <c r="BD7" t="n">
-        <v>-3.469210441184867e-05</v>
+        <v>0.0002241552580054318</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.0001660730600634208</v>
+        <v>-0.0006112424201776933</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.007655104771424198</v>
+        <v>-0.002746261682022855</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.002478939342940101</v>
+        <v>-0.001881133720173039</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
       </c>
       <c r="BI7" t="n">
-        <v>-0.0001568742189454298</v>
+        <v>0.0004124641930989381</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.001088387351877751</v>
+        <v>-0.001160767505276722</v>
       </c>
       <c r="BK7" t="n">
-        <v>-0.002200392648531824</v>
+        <v>-0.003526912705424124</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0.0002242192984285241</v>
+        <v>-0.0001153006909775933</v>
       </c>
       <c r="BM7" t="n">
-        <v>-0.0001227586708250295</v>
+        <v>-0.001206819437501672</v>
       </c>
       <c r="BN7" t="n">
-        <v>-0.001711719047466087</v>
+        <v>-0.0009342295851594573</v>
       </c>
       <c r="BO7" t="n">
-        <v>-9.945689127964785e-05</v>
+        <v>-0.001420938586043036</v>
       </c>
       <c r="BP7" t="n">
-        <v>-0.001233568335185225</v>
+        <v>-0.001763538941397374</v>
       </c>
       <c r="BQ7" t="n">
-        <v>-1.609269391698031e-05</v>
+        <v>-8.507704291669248e-05</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0.0004325867717112853</v>
+        <v>-0.0001380410273332355</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.0003622364697213276</v>
+        <v>-0.002020777120413209</v>
       </c>
       <c r="BT7" t="n">
-        <v>-6.487230934106857e-05</v>
+        <v>-0.001151467748076723</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.006058091938309734</v>
+        <v>0.005517717025435964</v>
       </c>
       <c r="BV7" t="n">
-        <v>-0.0007075461758280721</v>
+        <v>-0.0006038582172607776</v>
       </c>
       <c r="BW7" t="n">
-        <v>-0.002563248884359914</v>
+        <v>0.0004612433321769306</v>
       </c>
       <c r="BX7" t="n">
-        <v>-1.735508503992178e-05</v>
+        <v>0.0002181082057365169</v>
       </c>
       <c r="BY7" t="n">
-        <v>-0.0003304250693445976</v>
+        <v>-0.0001384317392593259</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.0001184707640610294</v>
+        <v>0.0001026571307436219</v>
       </c>
       <c r="CA7" t="n">
         <v>0</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.401397363314019e-05</v>
+        <v>-0.0002770872550304504</v>
       </c>
       <c r="CC7" t="n">
-        <v>-0.0008963900523390465</v>
+        <v>-0.000688614588284503</v>
       </c>
       <c r="CD7" t="n">
         <v>0</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.0006419936211330745</v>
+        <v>0.0006638493142284874</v>
       </c>
       <c r="CF7" t="n">
-        <v>-0.001611123269052989</v>
+        <v>-0.001471643933955474</v>
       </c>
       <c r="CG7" t="n">
-        <v>-0.0005368644276531054</v>
+        <v>-0.0004673447411168763</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.0001378359751895375</v>
+        <v>-0.0001892743656504492</v>
       </c>
       <c r="CI7" t="n">
-        <v>-0.002623253905428113</v>
+        <v>0.0001024746530907062</v>
       </c>
       <c r="CJ7" t="n">
-        <v>7.154905200008055e-05</v>
+        <v>-0.001993185601060277</v>
       </c>
       <c r="CK7" t="n">
-        <v>-0.0004074367686734526</v>
+        <v>0.001491313135224137</v>
       </c>
     </row>
     <row r="8">
@@ -2503,268 +2503,268 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001199571253926371</v>
+        <v>0.001530198841095426</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0009278145751508426</v>
+        <v>-0.001159936122925601</v>
       </c>
       <c r="E8" t="n">
-        <v>0.004198346913321635</v>
+        <v>0.00422783860946678</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0007957047062486982</v>
+        <v>0.001929483947659341</v>
       </c>
       <c r="G8" t="n">
-        <v>0.005247162649845682</v>
+        <v>0.003600057704791893</v>
       </c>
       <c r="H8" t="n">
-        <v>0.003340016997961881</v>
+        <v>0.007507853596055259</v>
       </c>
       <c r="I8" t="n">
-        <v>0.000437349922406316</v>
+        <v>0.0002169055571318301</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.001890445660156317</v>
+        <v>0.002415662045582842</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03071074070776039</v>
+        <v>0.03192121135855993</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02978792267809863</v>
+        <v>0.03888713036756571</v>
       </c>
       <c r="M8" t="n">
-        <v>0.005070512960937715</v>
+        <v>0.003341707954132861</v>
       </c>
       <c r="N8" t="n">
-        <v>0.002572226889221707</v>
+        <v>0.003868224237016923</v>
       </c>
       <c r="O8" t="n">
-        <v>0.009404835406574266</v>
+        <v>0.003942423465824454</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0182799671592775</v>
+        <v>0.0235481452974825</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01212004881636618</v>
+        <v>0.006068182554035911</v>
       </c>
       <c r="R8" t="n">
-        <v>0.003802883306042071</v>
+        <v>0.002022825079526203</v>
       </c>
       <c r="S8" t="n">
-        <v>0.003069626656773833</v>
+        <v>0.002381499088058203</v>
       </c>
       <c r="T8" t="n">
-        <v>0.002560881410182248</v>
+        <v>0.003573835230627692</v>
       </c>
       <c r="U8" t="n">
-        <v>0.002699345637816567</v>
+        <v>0.002181348438097275</v>
       </c>
       <c r="V8" t="n">
-        <v>7.241712262630318e-05</v>
+        <v>0.000230183727935615</v>
       </c>
       <c r="W8" t="n">
-        <v>0.00458889862355499</v>
+        <v>0.01038933906859864</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0001535971590418239</v>
+        <v>0.0004717824712534846</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.004263743052600436</v>
+        <v>0.002777546821128402</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.001352075036315734</v>
+        <v>0.002078289374693088</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.0009540338542761068</v>
+        <v>0.0002866399973551287</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.736126466261208e-05</v>
+        <v>0.0005356708267575088</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.007857817781549795</v>
+        <v>0.002568360645905296</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.0004239781838602601</v>
+        <v>0.004739251746691774</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.000291452163476405</v>
+        <v>-0.001263941959823944</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.003529538618175484</v>
+        <v>-0.0005123439020032234</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.0002321742423849471</v>
+        <v>0.0003877684151406296</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.0006457342641620234</v>
+        <v>-5.047478721995347e-05</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.001895919985870029</v>
+        <v>0.0009633179568381945</v>
       </c>
       <c r="AK8" t="n">
-        <v>-0.0005319498941987938</v>
+        <v>0.0008597756382733828</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.0001749499221967099</v>
+        <v>0.0001175906875457183</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.0002513347627257162</v>
+        <v>0.0008761837478481637</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.002862921530056964</v>
+        <v>0.002063011438124765</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.001068932445344695</v>
+        <v>0.0007304763791293967</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.0006757180232857013</v>
+        <v>0.000106816806545787</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.002556920617369868</v>
+        <v>0.002245371137173371</v>
       </c>
       <c r="AR8" t="n">
-        <v>2.106212200442547e-05</v>
+        <v>0.0006758404633986053</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.0001790840831014884</v>
+        <v>0.004384973359448222</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.001620313433360302</v>
+        <v>-0.001262439550777403</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.006274691751014689</v>
+        <v>0.001082825955503661</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.00102984380892242</v>
+        <v>0.0004022243325175839</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.002111735829916023</v>
+        <v>-0.0005719791753652421</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.001550110694436005</v>
+        <v>0.000960612692740498</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.003645132177640761</v>
+        <v>0.0002798062562401754</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.005153070687232298</v>
+        <v>0.001900864382074691</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.002596721784004505</v>
+        <v>0.001179084073820891</v>
       </c>
       <c r="BB8" t="n">
-        <v>-0.0004900423593665743</v>
+        <v>-0.001474163868305458</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.0002161111317773079</v>
+        <v>0.0009391338889822799</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.0007605439419576671</v>
+        <v>0.0007167611456296518</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.0009904351075618796</v>
+        <v>-3.490401396165077e-05</v>
       </c>
       <c r="BF8" t="n">
-        <v>-2.084855705131736e-05</v>
+        <v>-0.0006946835798868345</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.003123461266061858</v>
+        <v>0.001377381711991593</v>
       </c>
       <c r="BH8" t="n">
         <v>0</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.0002677373728948856</v>
+        <v>0.000948854345755179</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.002395538521289831</v>
+        <v>0.0005201073721306487</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.002650421073591294</v>
+        <v>-0.001162917407750735</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.0003310318574299975</v>
+        <v>0.0004938663947902766</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.0008874447025059073</v>
+        <v>-0.0003784736135008404</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.001188763106341037</v>
+        <v>0.0006783919597990128</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.008047971017701513</v>
+        <v>0.001282461055213024</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.001045229163872191</v>
+        <v>0.0001934635699499837</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.0003697040783285505</v>
+        <v>0.0001022369235550519</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.003314682454739687</v>
+        <v>0.0009212010001954014</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.001865629488565784</v>
+        <v>0.003276284824324363</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.0002421790497478815</v>
+        <v>-0.0004914874846650291</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.01104753080236405</v>
+        <v>0.009929936123968926</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.0005814264888756886</v>
+        <v>0.001342998032895978</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.0023481452402213</v>
+        <v>0.004654061305937734</v>
       </c>
       <c r="BX8" t="n">
-        <v>2.602359472588523e-05</v>
+        <v>0.0004361010870909482</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.001013208575327562</v>
+        <v>0.0003560121725555809</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.000260308209930768</v>
+        <v>0.0002571233549146762</v>
       </c>
       <c r="CA8" t="n">
         <v>0</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.001145761657526889</v>
+        <v>0.0001222832517746103</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.001380848474700241</v>
+        <v>0.0001245547950475712</v>
       </c>
       <c r="CD8" t="n">
-        <v>0</v>
+        <v>4.926108374384564e-05</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.001073164109276237</v>
+        <v>0.001421006649934359</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.001420793002705892</v>
+        <v>-0.0004511840359232216</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.0009208008265214119</v>
+        <v>0.002846126629359044</v>
       </c>
       <c r="CH8" t="n">
-        <v>7.809788267963691e-05</v>
+        <v>0.0004408713692946154</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.001199105286945973</v>
+        <v>0.001632221256659228</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.004661657375678213</v>
+        <v>0.0003511680115654392</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.0008254811417162528</v>
+        <v>0.002141998221286795</v>
       </c>
     </row>
     <row r="9">
@@ -2774,268 +2774,268 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.007074504442925522</v>
+        <v>0.005306685044796755</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.007787732598208075</v>
+        <v>0.004579630895420339</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01201970443349754</v>
+        <v>0.005099931082012454</v>
       </c>
       <c r="F9" t="n">
-        <v>0.00285714285714288</v>
+        <v>0.005982019363762081</v>
       </c>
       <c r="G9" t="n">
-        <v>0.008542713567839167</v>
+        <v>0.007619047619047636</v>
       </c>
       <c r="H9" t="n">
-        <v>0.009466848940533169</v>
+        <v>0.0120749479528105</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001018062397372743</v>
+        <v>0.0004442925495556582</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0002792321116928731</v>
+        <v>0.004397905759162268</v>
       </c>
       <c r="K9" t="n">
-        <v>0.05838429353073701</v>
+        <v>0.0439597315436242</v>
       </c>
       <c r="L9" t="n">
-        <v>0.05842281879194635</v>
+        <v>0.06238255033557048</v>
       </c>
       <c r="M9" t="n">
-        <v>0.007348993288590655</v>
+        <v>0.005809128630705374</v>
       </c>
       <c r="N9" t="n">
-        <v>0.005221674876847304</v>
+        <v>0.00607217210270643</v>
       </c>
       <c r="O9" t="n">
-        <v>0.01661641541038522</v>
+        <v>0.01530377668308703</v>
       </c>
       <c r="P9" t="n">
-        <v>0.04805369127516783</v>
+        <v>0.0409060402684564</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.03451559934318556</v>
+        <v>0.04620689655172418</v>
       </c>
       <c r="R9" t="n">
-        <v>0.009501025290499</v>
+        <v>0.008955223880597041</v>
       </c>
       <c r="S9" t="n">
-        <v>0.004853041695146987</v>
+        <v>0.005648604269293933</v>
       </c>
       <c r="T9" t="n">
-        <v>0.006910994764397949</v>
+        <v>0.006443831840110326</v>
       </c>
       <c r="U9" t="n">
-        <v>0.005427135678391926</v>
+        <v>0.00801313628899838</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0003112033195020736</v>
+        <v>0.0004926108374384453</v>
       </c>
       <c r="W9" t="n">
-        <v>0.02732539427100095</v>
+        <v>0.02404248471194075</v>
       </c>
       <c r="X9" t="n">
-        <v>0.008787043418332119</v>
+        <v>0.004514128187456989</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.00676613462873008</v>
+        <v>0.0079458709229701</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.002397372742200332</v>
+        <v>0.004649548924358049</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.003119868637110024</v>
+        <v>0.001802381718699686</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0007224958949096805</v>
+        <v>0.0007860560492139124</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.01714087439278282</v>
+        <v>0.01617493925720239</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.009983249581239473</v>
+        <v>0.006915629322268302</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.004589614740368475</v>
+        <v>0.0106478290833908</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.006616126809097145</v>
+        <v>0.007925568573397679</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.001210235131396953</v>
+        <v>0.001158673962021206</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.001884816753926732</v>
+        <v>0.0003862246540070613</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.006758931445123883</v>
+        <v>0.003549276361130305</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.0003075871496924454</v>
+        <v>0.005912863070539398</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.001041305102394974</v>
+        <v>0.001041305102395051</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.0007952973720608547</v>
+        <v>0.002498265093684871</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.006371100164203625</v>
+        <v>0.009892398472752573</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.003785594639865975</v>
+        <v>0.008097863542384575</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.001196172248803862</v>
+        <v>0.002756719503790528</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.005274115197779361</v>
+        <v>0.004602510460251019</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.002495894909688023</v>
+        <v>0.002914572864321618</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.008144499178981945</v>
+        <v>0.006696738376127653</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.007462686567164212</v>
+        <v>0.0007860560492139012</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.01083743842364533</v>
+        <v>0.007818791946308756</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.00266009852216752</v>
+        <v>0.0009993108201240663</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.01141490088858512</v>
+        <v>0.001145435612634538</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.003551088777219413</v>
+        <v>0.001769604441360084</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.005342774380431259</v>
+        <v>0.001839000693962467</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.008167539267015734</v>
+        <v>0.008848022206800777</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.01507537688442206</v>
+        <v>0.006767169179229504</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.01708542713567834</v>
+        <v>0.01266331658291458</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.000410116199589905</v>
+        <v>0.002791461412151086</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.001970443349753703</v>
+        <v>0.0008046346958480388</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.001572112098427925</v>
+        <v>0.000361247947454868</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.003979057591623059</v>
+        <v>0.006331658291457321</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.01228740020826103</v>
+        <v>0.009706083390293895</v>
       </c>
       <c r="BH9" t="n">
         <v>0</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.003152709359605932</v>
+        <v>0.002955665024630549</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.004154103852596303</v>
+        <v>0.003875205254515612</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.006298157453936304</v>
+        <v>0.0001040943789034854</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.001512713228194373</v>
+        <v>0.0007724493080141226</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.005828970331588157</v>
+        <v>0.003782095766828553</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.007364746945898804</v>
+        <v>0.004677137870855086</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.01114093959731547</v>
+        <v>0.005335570469798689</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.005418719211822654</v>
+        <v>0.006823302220791727</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.0007224958949097026</v>
+        <v>0.0002013422818792354</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.005996649916247887</v>
+        <v>0.004094378903539153</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.004489112227805658</v>
+        <v>0.005032974661575884</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.002904989747095044</v>
+        <v>-0.0002010050251256223</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.01896147403685089</v>
+        <v>0.01893369788106627</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.00433877125997918</v>
+        <v>0.003630705394190858</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.01731993299832492</v>
+        <v>0.01030201342281882</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.0001745200698080485</v>
+        <v>0.0007402639201802175</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.003075871496924154</v>
+        <v>0.00383006115223683</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.006015037593984984</v>
+        <v>0.002864499517219155</v>
       </c>
       <c r="CA9" t="n">
-        <v>6.891798759474099e-05</v>
+        <v>0</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.003417634996582408</v>
+        <v>0.001778523489932893</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.001879699248120326</v>
+        <v>0.005939597315436263</v>
       </c>
       <c r="CD9" t="n">
-        <v>0</v>
+        <v>0.0003112033195020736</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.002699931647300102</v>
+        <v>0.003724832214765117</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.00555362721277336</v>
+        <v>0.0003417634996581986</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.004860426929392448</v>
+        <v>0.003852596314907897</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.001037344398340245</v>
+        <v>0.002443280977312356</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.005341144038594037</v>
+        <v>0.004731252011586695</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.006767169179229438</v>
+        <v>0.009899328859060419</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.00482758620689655</v>
+        <v>0.009005235602094175</v>
       </c>
     </row>
   </sheetData>
